--- a/artfynd/S 5489-2021 artfynd.xlsx
+++ b/artfynd/S 5489-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74116640</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74479303</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73968211</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
           <t>JSN0208 Ryningsnäs NVI</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114762060</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
           <t>JSN0208 Ryningsnäs NVI</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114762041</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
           <t>JSN0208 Ryningsnäs NVI</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114762042</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
           <t>JSN0208 Ryningsnäs NVI</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114762026</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1530,6 +1570,11 @@
           <t>JSN0208 Ryningsnäs NVI</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114762040</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
           <t>JSN0208 Ryningsnäs NVI</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114762056</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1740,6 +1790,11 @@
           <t>JSN0208 Ryningsnäs NVI</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114762049</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1845,6 +1900,11 @@
           <t>JSN0208 Ryningsnäs NVI</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114762059</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1950,6 +2010,11 @@
           <t>JSN0208 Ryningsnäs NVI</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114762048</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2055,6 +2120,11 @@
           <t>JSN0208 Ryningsnäs NVI</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114762001</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2160,6 +2230,11 @@
           <t>JSN0208 Ryningsnäs NVI</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114761998</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2265,6 +2340,11 @@
           <t>JSN0208 Ryningsnäs NVI</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114762000</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2370,6 +2450,11 @@
           <t>JSN0208 Ryningsnäs NVI</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114762002</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2473,6 +2558,11 @@
       <c r="AY18" t="inlineStr">
         <is>
           <t>JSN0208 Ryningsnäs NVI</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114761997</t>
         </is>
       </c>
     </row>
@@ -2582,6 +2672,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99937797</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2701,6 +2796,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53789989</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2797,6 +2897,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53789972</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2908,6 +3013,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74767701</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3019,6 +3129,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74574118</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3130,6 +3245,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74579265</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3239,6 +3359,11 @@
       <c r="AY25" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75016470</t>
         </is>
       </c>
     </row>
@@ -3348,8 +3473,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113932917</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>